--- a/Analysis/tables/B1_descriptive_stats.xlsx
+++ b/Analysis/tables/B1_descriptive_stats.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,37 +1137,185 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>team_early_cs_10</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19520</v>
+      </c>
+      <c r="C20" t="n">
+        <v>270.6006148303202</v>
+      </c>
+      <c r="D20" t="n">
+        <v>25.76547242126393</v>
+      </c>
+      <c r="E20" t="n">
+        <v>157.0000000596046</v>
+      </c>
+      <c r="F20" t="n">
+        <v>253.000000089407</v>
+      </c>
+      <c r="G20" t="n">
+        <v>270.7500000596046</v>
+      </c>
+      <c r="H20" t="n">
+        <v>288.000000089407</v>
+      </c>
+      <c r="I20" t="n">
+        <v>379.000000089407</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.02996317944904692</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-0.02878913398891303</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>team_early_gold_adv</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>19520</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.08350409836065574</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1277614329233063</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.518630390797077</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.300222598813551</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>team_early_takedowns</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>19520</v>
+      </c>
+      <c r="C22" t="n">
+        <v>24.65414959016394</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9.944799136350081</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>17</v>
+      </c>
+      <c r="G22" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" t="n">
+        <v>31</v>
+      </c>
+      <c r="I22" t="n">
+        <v>75</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4379800146240332</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.09079017559247671</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>avg_skill_index</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>19520</v>
+      </c>
+      <c r="C23" t="n">
+        <v>67.53626024590164</v>
+      </c>
+      <c r="D23" t="n">
+        <v>39.42307795588846</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>84</v>
+      </c>
+      <c r="I23" t="n">
+        <v>370.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.609973359152843</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.647064198958457</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>win</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>19520</v>
-      </c>
-      <c r="C20" t="n">
+      <c r="B24" t="n">
+        <v>19520</v>
+      </c>
+      <c r="C24" t="n">
         <v>0.5</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D24" t="n">
         <v>0.5000128078691569</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
         <v>0.5</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H24" t="n">
         <v>1</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>-2.000204949531178</v>
       </c>
     </row>
